--- a/summer_camps/046_summer_camp_waitlist_form--summer_camps.xlsx
+++ b/summer_camps/046_summer_camp_waitlist_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
